--- a/data/intermediate/Ani_reduced.xlsx
+++ b/data/intermediate/Ani_reduced.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="1429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1954" uniqueCount="1426">
   <si>
     <t>#</t>
   </si>
@@ -102,7 +102,7 @@
     <t>Biotin synthase</t>
   </si>
   <si>
-    <t>2 Proton[m] + Dethiobiotin[m] + Sulfur[m] + 2 S-Adenosyl-L-methionine[m] =&gt; Biotin[m] + 2 L-Methionine[m] + 2 Deoxyadenosine[m]</t>
+    <t>Dethiobiotin[m] + Sulfur[m] + 2 S-Adenosyl-L-methionine[m] =&gt; Biotin[m] + 2 L-Methionine[m] + 2 Deoxyadenosine[m]</t>
   </si>
   <si>
     <t>2.8.1.6</t>
@@ -276,7 +276,7 @@
     <t>Ubiquinol-cytochrome c reductase</t>
   </si>
   <si>
-    <t>2 Ferricytochrome c[m] + 4 Proton (energy metabolism)[m] + Ubiquinol[m] =&gt; 2 Ferrocytochrome c[m] + 4 Proton (energy metabolism)[c] + Ubiquinone[m] + 2 Proton[m]</t>
+    <t>2 Ferricytochrome c[m] + 4 Proton (energy metabolism)[m] + Ubiquinol[m] =&gt; 2 Ferrocytochrome c[m] + 4 Proton (energy metabolism)[c] + Ubiquinone[m]</t>
   </si>
   <si>
     <t>1.10.2.2</t>
@@ -291,7 +291,7 @@
     <t>Cytochrome c oxidase subunit I (cox5)</t>
   </si>
   <si>
-    <t>2 Ferrocytochrome c[m] + 4 Proton (energy metabolism)[m] + 0.5 Oxygen[m] + 2 Proton[m] =&gt; 2 Ferricytochrome c[m] + 4 Proton (energy metabolism)[c] + Water[m]</t>
+    <t>2 Ferrocytochrome c[m] + 4 Proton (energy metabolism)[m] + 0.5 Oxygen[m] =&gt; 2 Ferricytochrome c[m] + 4 Proton (energy metabolism)[c] + Water[m]</t>
   </si>
   <si>
     <t>1.9.3.1</t>
@@ -3547,15 +3547,6 @@
   </si>
   <si>
     <t>VAL[m]</t>
-  </si>
-  <si>
-    <t>Proton[m]</t>
-  </si>
-  <si>
-    <t>Proton</t>
-  </si>
-  <si>
-    <t>H[m]</t>
   </si>
   <si>
     <t>L-Rhamnonic acid[c]</t>
@@ -10486,16 +10477,16 @@
         <v>1178</v>
       </c>
       <c r="E198" t="s" s="3">
-        <v>924</v>
+        <v>1179</v>
       </c>
       <c r="F198" t="s" s="3">
-        <v>925</v>
+        <v>1180</v>
       </c>
       <c r="H198" t="s" s="3">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="I198" t="s" s="3">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="J198" t="e" s="3">
         <v>#NUM!</v>
@@ -10503,22 +10494,22 @@
     </row>
     <row r="199">
       <c r="B199" t="s" s="3">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="C199" t="s" s="3">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="E199" t="s" s="3">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="F199" t="s" s="3">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="H199" t="s" s="3">
         <v>334</v>
       </c>
       <c r="I199" t="s" s="3">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="J199" t="e" s="3">
         <v>#NUM!</v>
@@ -10526,22 +10517,22 @@
     </row>
     <row r="200">
       <c r="B200" t="s" s="3">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="C200" t="s" s="3">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="E200" t="s" s="3">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="F200" t="s" s="3">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="H200" t="s" s="3">
         <v>334</v>
       </c>
       <c r="I200" t="s" s="3">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="J200" t="e" s="3">
         <v>#NUM!</v>
@@ -10549,22 +10540,22 @@
     </row>
     <row r="201">
       <c r="B201" t="s" s="3">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="C201" t="s" s="3">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="E201" t="s" s="3">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="F201" t="s" s="3">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="H201" t="s" s="3">
         <v>334</v>
       </c>
       <c r="I201" t="s" s="3">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="J201" t="e" s="3">
         <v>#NUM!</v>
@@ -10572,22 +10563,22 @@
     </row>
     <row r="202">
       <c r="B202" t="s" s="3">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="C202" t="s" s="3">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E202" t="s" s="3">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="F202" t="s" s="3">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="H202" t="s" s="3">
         <v>334</v>
       </c>
       <c r="I202" t="s" s="3">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="J202" t="e" s="3">
         <v>#NUM!</v>
@@ -10595,22 +10586,22 @@
     </row>
     <row r="203">
       <c r="B203" t="s" s="3">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="C203" t="s" s="3">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="E203" t="s" s="3">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F203" t="s" s="3">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="H203" t="s" s="3">
         <v>334</v>
       </c>
       <c r="I203" t="s" s="3">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="J203" t="e" s="3">
         <v>#NUM!</v>
@@ -10618,22 +10609,22 @@
     </row>
     <row r="204">
       <c r="B204" t="s" s="3">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C204" t="s" s="3">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="E204" t="s" s="3">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="F204" t="s" s="3">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="H204" t="s" s="3">
         <v>334</v>
       </c>
       <c r="I204" t="s" s="3">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="J204" t="e" s="3">
         <v>#NUM!</v>
@@ -10641,22 +10632,19 @@
     </row>
     <row r="205">
       <c r="B205" t="s" s="3">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="C205" t="s" s="3">
-        <v>1211</v>
-      </c>
-      <c r="E205" t="s" s="3">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="F205" t="s" s="3">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H205" t="s" s="3">
         <v>334</v>
       </c>
       <c r="I205" t="s" s="3">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="J205" t="e" s="3">
         <v>#NUM!</v>
@@ -10664,19 +10652,22 @@
     </row>
     <row r="206">
       <c r="B206" t="s" s="3">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="C206" t="s" s="3">
-        <v>1216</v>
+        <v>1217</v>
+      </c>
+      <c r="E206" t="s" s="3">
+        <v>1218</v>
       </c>
       <c r="F206" t="s" s="3">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="H206" t="s" s="3">
         <v>334</v>
       </c>
       <c r="I206" t="s" s="3">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="J206" t="e" s="3">
         <v>#NUM!</v>
@@ -10684,22 +10675,22 @@
     </row>
     <row r="207">
       <c r="B207" t="s" s="3">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="C207" t="s" s="3">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E207" t="s" s="3">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="F207" t="s" s="3">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="H207" t="s" s="3">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="I207" t="s" s="3">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="J207" t="e" s="3">
         <v>#NUM!</v>
@@ -10707,22 +10698,22 @@
     </row>
     <row r="208">
       <c r="B208" t="s" s="3">
+        <v>1226</v>
+      </c>
+      <c r="C208" t="s" s="3">
+        <v>1222</v>
+      </c>
+      <c r="E208" t="s" s="3">
+        <v>1223</v>
+      </c>
+      <c r="F208" t="s" s="3">
         <v>1224</v>
       </c>
-      <c r="C208" t="s" s="3">
-        <v>1225</v>
-      </c>
-      <c r="E208" t="s" s="3">
-        <v>1226</v>
-      </c>
-      <c r="F208" t="s" s="3">
+      <c r="H208" t="s" s="3">
+        <v>334</v>
+      </c>
+      <c r="I208" t="s" s="3">
         <v>1227</v>
-      </c>
-      <c r="H208" t="s" s="3">
-        <v>328</v>
-      </c>
-      <c r="I208" t="s" s="3">
-        <v>1228</v>
       </c>
       <c r="J208" t="e" s="3">
         <v>#NUM!</v>
@@ -10730,22 +10721,22 @@
     </row>
     <row r="209">
       <c r="B209" t="s" s="3">
+        <v>1228</v>
+      </c>
+      <c r="C209" t="s" s="3">
         <v>1229</v>
       </c>
-      <c r="C209" t="s" s="3">
-        <v>1225</v>
-      </c>
       <c r="E209" t="s" s="3">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="F209" t="s" s="3">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="H209" t="s" s="3">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="I209" t="s" s="3">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="J209" t="e" s="3">
         <v>#NUM!</v>
@@ -10753,22 +10744,22 @@
     </row>
     <row r="210">
       <c r="B210" t="s" s="3">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="C210" t="s" s="3">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="E210" t="s" s="3">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="F210" t="s" s="3">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="H210" t="s" s="3">
         <v>328</v>
       </c>
       <c r="I210" t="s" s="3">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="J210" t="e" s="3">
         <v>#NUM!</v>
@@ -10776,22 +10767,22 @@
     </row>
     <row r="211">
       <c r="B211" t="s" s="3">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="C211" t="s" s="3">
-        <v>1237</v>
+        <v>411</v>
       </c>
       <c r="E211" t="s" s="3">
+        <v>1239</v>
+      </c>
+      <c r="F211" t="s" s="3">
+        <v>1240</v>
+      </c>
+      <c r="H211" t="s" s="3">
+        <v>653</v>
+      </c>
+      <c r="I211" t="s" s="3">
         <v>1238</v>
-      </c>
-      <c r="F211" t="s" s="3">
-        <v>1239</v>
-      </c>
-      <c r="H211" t="s" s="3">
-        <v>328</v>
-      </c>
-      <c r="I211" t="s" s="3">
-        <v>1240</v>
       </c>
       <c r="J211" t="e" s="3">
         <v>#NUM!</v>
@@ -10802,7 +10793,7 @@
         <v>1241</v>
       </c>
       <c r="C212" t="s" s="3">
-        <v>411</v>
+        <v>392</v>
       </c>
       <c r="E212" t="s" s="3">
         <v>1242</v>
@@ -10825,19 +10816,19 @@
         <v>1244</v>
       </c>
       <c r="C213" t="s" s="3">
-        <v>392</v>
+        <v>1245</v>
       </c>
       <c r="E213" t="s" s="3">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="F213" t="s" s="3">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="H213" t="s" s="3">
-        <v>653</v>
+        <v>340</v>
       </c>
       <c r="I213" t="s" s="3">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="J213" t="e" s="3">
         <v>#NUM!</v>
@@ -10845,22 +10836,22 @@
     </row>
     <row r="214">
       <c r="B214" t="s" s="3">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="C214" t="s" s="3">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="E214" t="s" s="3">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="F214" t="s" s="3">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="H214" t="s" s="3">
         <v>340</v>
       </c>
       <c r="I214" t="s" s="3">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="J214" t="e" s="3">
         <v>#NUM!</v>
@@ -10868,13 +10859,13 @@
     </row>
     <row r="215">
       <c r="B215" t="s" s="3">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="C215" t="s" s="3">
-        <v>1253</v>
+        <v>1130</v>
       </c>
       <c r="E215" t="s" s="3">
-        <v>1254</v>
+        <v>1131</v>
       </c>
       <c r="F215" t="s" s="3">
         <v>1255</v>
@@ -10894,19 +10885,19 @@
         <v>1257</v>
       </c>
       <c r="C216" t="s" s="3">
-        <v>1130</v>
+        <v>1258</v>
       </c>
       <c r="E216" t="s" s="3">
-        <v>1131</v>
+        <v>1259</v>
       </c>
       <c r="F216" t="s" s="3">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="H216" t="s" s="3">
         <v>340</v>
       </c>
       <c r="I216" t="s" s="3">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="J216" t="e" s="3">
         <v>#NUM!</v>
@@ -10914,22 +10905,22 @@
     </row>
     <row r="217">
       <c r="B217" t="s" s="3">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="C217" t="s" s="3">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="E217" t="s" s="3">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="F217" t="s" s="3">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="H217" t="s" s="3">
         <v>340</v>
       </c>
       <c r="I217" t="s" s="3">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="J217" t="e" s="3">
         <v>#NUM!</v>
@@ -10937,22 +10928,22 @@
     </row>
     <row r="218">
       <c r="B218" t="s" s="3">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="C218" t="s" s="3">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="E218" t="s" s="3">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="F218" t="s" s="3">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="H218" t="s" s="3">
         <v>340</v>
       </c>
       <c r="I218" t="s" s="3">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="J218" t="e" s="3">
         <v>#NUM!</v>
@@ -10960,22 +10951,22 @@
     </row>
     <row r="219">
       <c r="B219" t="s" s="3">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="C219" t="s" s="3">
-        <v>1271</v>
+        <v>994</v>
       </c>
       <c r="E219" t="s" s="3">
-        <v>1272</v>
-      </c>
-      <c r="F219" t="s" s="3">
+        <v>995</v>
+      </c>
+      <c r="G219" t="s" s="3">
+        <v>996</v>
+      </c>
+      <c r="H219" t="s" s="3">
+        <v>653</v>
+      </c>
+      <c r="I219" t="s" s="3">
         <v>1273</v>
-      </c>
-      <c r="H219" t="s" s="3">
-        <v>340</v>
-      </c>
-      <c r="I219" t="s" s="3">
-        <v>1274</v>
       </c>
       <c r="J219" t="e" s="3">
         <v>#NUM!</v>
@@ -10983,22 +10974,22 @@
     </row>
     <row r="220">
       <c r="B220" t="s" s="3">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C220" t="s" s="3">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="E220" t="s" s="3">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="G220" t="s" s="3">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="H220" t="s" s="3">
         <v>653</v>
       </c>
       <c r="I220" t="s" s="3">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="J220" t="e" s="3">
         <v>#NUM!</v>
@@ -11006,22 +10997,19 @@
     </row>
     <row r="221">
       <c r="B221" t="s" s="3">
+        <v>1275</v>
+      </c>
+      <c r="C221" t="s" s="3">
+        <v>1276</v>
+      </c>
+      <c r="F221" t="s" s="3">
         <v>1277</v>
-      </c>
-      <c r="C221" t="s" s="3">
-        <v>999</v>
-      </c>
-      <c r="E221" t="s" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G221" t="s" s="3">
-        <v>1001</v>
       </c>
       <c r="H221" t="s" s="3">
         <v>653</v>
       </c>
       <c r="I221" t="s" s="3">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="J221" t="e" s="3">
         <v>#NUM!</v>
@@ -11029,19 +11017,22 @@
     </row>
     <row r="222">
       <c r="B222" t="s" s="3">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="C222" t="s" s="3">
-        <v>1279</v>
+        <v>1280</v>
+      </c>
+      <c r="E222" t="s" s="3">
+        <v>1281</v>
       </c>
       <c r="F222" t="s" s="3">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="H222" t="s" s="3">
         <v>653</v>
       </c>
       <c r="I222" t="s" s="3">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="J222" t="e" s="3">
         <v>#NUM!</v>
@@ -11049,22 +11040,19 @@
     </row>
     <row r="223">
       <c r="B223" t="s" s="3">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C223" t="s" s="3">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="E223" t="s" s="3">
+        <v>1286</v>
+      </c>
+      <c r="H223" t="s" s="3">
+        <v>340</v>
+      </c>
+      <c r="I223" t="s" s="3">
         <v>1284</v>
-      </c>
-      <c r="F223" t="s" s="3">
-        <v>1285</v>
-      </c>
-      <c r="H223" t="s" s="3">
-        <v>653</v>
-      </c>
-      <c r="I223" t="s" s="3">
-        <v>1286</v>
       </c>
       <c r="J223" t="e" s="3">
         <v>#NUM!</v>
@@ -11080,11 +11068,14 @@
       <c r="E224" t="s" s="3">
         <v>1289</v>
       </c>
+      <c r="G224" t="s" s="3">
+        <v>1290</v>
+      </c>
       <c r="H224" t="s" s="3">
         <v>340</v>
       </c>
       <c r="I224" t="s" s="3">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="J224" t="e" s="3">
         <v>#NUM!</v>
@@ -11092,22 +11083,22 @@
     </row>
     <row r="225">
       <c r="B225" t="s" s="3">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="C225" t="s" s="3">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="E225" t="s" s="3">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="G225" t="s" s="3">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="H225" t="s" s="3">
         <v>340</v>
       </c>
       <c r="I225" t="s" s="3">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="J225" t="e" s="3">
         <v>#NUM!</v>
@@ -11115,22 +11106,22 @@
     </row>
     <row r="226">
       <c r="B226" t="s" s="3">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="C226" t="s" s="3">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="E226" t="s" s="3">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="G226" t="s" s="3">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="H226" t="s" s="3">
         <v>340</v>
       </c>
       <c r="I226" t="s" s="3">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="J226" t="e" s="3">
         <v>#NUM!</v>
@@ -11138,22 +11129,22 @@
     </row>
     <row r="227">
       <c r="B227" t="s" s="3">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="C227" t="s" s="3">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="E227" t="s" s="3">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="G227" t="s" s="3">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="H227" t="s" s="3">
         <v>340</v>
       </c>
       <c r="I227" t="s" s="3">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="J227" t="e" s="3">
         <v>#NUM!</v>
@@ -11161,22 +11152,22 @@
     </row>
     <row r="228">
       <c r="B228" t="s" s="3">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="C228" t="s" s="3">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="E228" t="s" s="3">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="G228" t="s" s="3">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="H228" t="s" s="3">
         <v>340</v>
       </c>
       <c r="I228" t="s" s="3">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="J228" t="e" s="3">
         <v>#NUM!</v>
@@ -11184,22 +11175,22 @@
     </row>
     <row r="229">
       <c r="B229" t="s" s="3">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="C229" t="s" s="3">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="E229" t="s" s="3">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="G229" t="s" s="3">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="H229" t="s" s="3">
         <v>340</v>
       </c>
       <c r="I229" t="s" s="3">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="J229" t="e" s="3">
         <v>#NUM!</v>
@@ -11207,22 +11198,22 @@
     </row>
     <row r="230">
       <c r="B230" t="s" s="3">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="C230" t="s" s="3">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="E230" t="s" s="3">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="G230" t="s" s="3">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="H230" t="s" s="3">
         <v>340</v>
       </c>
       <c r="I230" t="s" s="3">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="J230" t="e" s="3">
         <v>#NUM!</v>
@@ -11230,47 +11221,24 @@
     </row>
     <row r="231">
       <c r="B231" t="s" s="3">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="C231" t="s" s="3">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="E231" t="s" s="3">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="G231" t="s" s="3">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="H231" t="s" s="3">
         <v>340</v>
       </c>
       <c r="I231" t="s" s="3">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="J231" t="e" s="3">
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="B232" t="s" s="3">
-        <v>1325</v>
-      </c>
-      <c r="C232" t="s" s="3">
-        <v>1326</v>
-      </c>
-      <c r="E232" t="s" s="3">
-        <v>1327</v>
-      </c>
-      <c r="G232" t="s" s="3">
-        <v>1328</v>
-      </c>
-      <c r="H232" t="s" s="3">
-        <v>340</v>
-      </c>
-      <c r="I232" t="s" s="3">
-        <v>1329</v>
-      </c>
-      <c r="J232" t="e" s="3">
         <v>#NUM!</v>
       </c>
     </row>
@@ -11296,13 +11264,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="6">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="C1" t="s" s="6">
         <v>2</v>
       </c>
       <c r="D1" t="s" s="6">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="E1" t="s" s="6">
         <v>10</v>
@@ -11313,7 +11281,7 @@
         <v>653</v>
       </c>
       <c r="C2" t="s" s="5">
-        <v>1332</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="3">
@@ -11321,7 +11289,7 @@
         <v>334</v>
       </c>
       <c r="C3" t="s" s="5">
-        <v>1333</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="4">
@@ -11329,7 +11297,7 @@
         <v>340</v>
       </c>
       <c r="C4" t="s" s="5">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="5">
@@ -11337,7 +11305,7 @@
         <v>328</v>
       </c>
       <c r="C5" t="s" s="5">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
   </sheetData>
@@ -11368,7 +11336,7 @@
         <v>10</v>
       </c>
       <c r="D1" t="s" s="8">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="E1" t="s" s="8">
         <v>9</v>
@@ -11376,18 +11344,18 @@
     </row>
     <row r="2">
       <c r="B2" t="s" s="7">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="D2" t="s" s="7">
-        <v>1338</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="s" s="7">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="D3" t="s" s="7">
-        <v>1340</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="4">
@@ -11395,7 +11363,7 @@
         <v>291</v>
       </c>
       <c r="D4" t="s" s="7">
-        <v>1341</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="5">
@@ -11403,7 +11371,7 @@
         <v>315</v>
       </c>
       <c r="D5" t="s" s="7">
-        <v>1342</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="6">
@@ -11411,7 +11379,7 @@
         <v>120</v>
       </c>
       <c r="D6" t="s" s="7">
-        <v>1343</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="7">
@@ -11419,79 +11387,79 @@
         <v>272</v>
       </c>
       <c r="D7" t="s" s="7">
-        <v>1344</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="s" s="7">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="D8" t="s" s="7">
-        <v>1346</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s" s="7">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="D9" t="s" s="7">
-        <v>1348</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s" s="7">
-        <v>1349</v>
+        <v>1346</v>
       </c>
       <c r="D10" t="s" s="7">
-        <v>1350</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s" s="7">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="D11" t="s" s="7">
-        <v>1352</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s" s="7">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="D12" t="s" s="7">
-        <v>1354</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s" s="7">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="D13" t="s" s="7">
-        <v>1356</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="s" s="7">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="D14" t="s" s="7">
-        <v>1358</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s" s="7">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="D15" t="s" s="7">
-        <v>1360</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="s" s="7">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="D16" t="s" s="7">
-        <v>1362</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="17">
@@ -11499,79 +11467,79 @@
         <v>20</v>
       </c>
       <c r="D17" t="s" s="7">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="s" s="7">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="D18" t="s" s="7">
-        <v>1365</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s" s="7">
-        <v>1366</v>
+        <v>1363</v>
       </c>
       <c r="D19" t="s" s="7">
-        <v>1367</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="s" s="7">
-        <v>1368</v>
+        <v>1365</v>
       </c>
       <c r="D20" t="s" s="7">
-        <v>1369</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s" s="7">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="D21" t="s" s="7">
-        <v>1371</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s" s="7">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="D22" t="s" s="7">
-        <v>1373</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s" s="7">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="D23" t="s" s="7">
-        <v>1375</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="s" s="7">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="D24" t="s" s="7">
-        <v>1377</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="s" s="7">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="D25" t="s" s="7">
-        <v>1379</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="s" s="7">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="D26" t="s" s="7">
-        <v>1381</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="27">
@@ -11579,31 +11547,31 @@
         <v>88</v>
       </c>
       <c r="D27" t="s" s="7">
-        <v>1382</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="s" s="7">
-        <v>1383</v>
+        <v>1380</v>
       </c>
       <c r="D28" t="s" s="7">
-        <v>1384</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s" s="7">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="D29" t="s" s="7">
-        <v>1386</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s" s="7">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="D30" t="s" s="7">
-        <v>1388</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="31">
@@ -11611,7 +11579,7 @@
         <v>115</v>
       </c>
       <c r="D31" t="s" s="7">
-        <v>1389</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="32">
@@ -11619,7 +11587,7 @@
         <v>239</v>
       </c>
       <c r="D32" t="s" s="7">
-        <v>1390</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="33">
@@ -11627,7 +11595,7 @@
         <v>262</v>
       </c>
       <c r="D33" t="s" s="7">
-        <v>1391</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="34">
@@ -11635,23 +11603,23 @@
         <v>302</v>
       </c>
       <c r="D34" t="s" s="7">
-        <v>1392</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="s" s="7">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="D35" t="s" s="7">
-        <v>1394</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="s" s="7">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="D36" t="s" s="7">
-        <v>1396</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="37">
@@ -11659,23 +11627,23 @@
         <v>306</v>
       </c>
       <c r="D37" t="s" s="7">
-        <v>1397</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="s" s="7">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="D38" t="s" s="7">
-        <v>1399</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="s" s="7">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="D39" t="s" s="7">
-        <v>1401</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="40">
@@ -11683,7 +11651,7 @@
         <v>281</v>
       </c>
       <c r="D40" t="s" s="7">
-        <v>1402</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="41">
@@ -11691,31 +11659,31 @@
         <v>311</v>
       </c>
       <c r="D41" t="s" s="7">
-        <v>1403</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="s" s="7">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="D42" t="s" s="7">
-        <v>1405</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="s" s="7">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="D43" t="s" s="7">
-        <v>1407</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="s" s="7">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="D44" t="s" s="7">
-        <v>1409</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="45">
@@ -11723,31 +11691,31 @@
         <v>30</v>
       </c>
       <c r="D45" t="s" s="7">
-        <v>1410</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="s" s="7">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="D46" t="s" s="7">
-        <v>1412</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="s" s="7">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="D47" t="s" s="7">
-        <v>1414</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="s" s="7">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="D48" t="s" s="7">
-        <v>1416</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="49">
@@ -11755,7 +11723,7 @@
         <v>286</v>
       </c>
       <c r="D49" t="s" s="7">
-        <v>1417</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="50">
@@ -11763,7 +11731,7 @@
         <v>295</v>
       </c>
       <c r="D50" t="s" s="7">
-        <v>1418</v>
+        <v>1415</v>
       </c>
     </row>
   </sheetData>
@@ -11800,36 +11768,36 @@
         <v>2</v>
       </c>
       <c r="D1" t="s" s="10">
+        <v>1416</v>
+      </c>
+      <c r="E1" t="s" s="10">
+        <v>1417</v>
+      </c>
+      <c r="F1" t="s" s="10">
+        <v>1418</v>
+      </c>
+      <c r="G1" t="s" s="10">
         <v>1419</v>
       </c>
-      <c r="E1" t="s" s="10">
+      <c r="H1" t="s" s="10">
         <v>1420</v>
       </c>
-      <c r="F1" t="s" s="10">
+      <c r="I1" t="s" s="10">
         <v>1421</v>
       </c>
-      <c r="G1" t="s" s="10">
+      <c r="J1" t="s" s="10">
         <v>1422</v>
       </c>
-      <c r="H1" t="s" s="10">
+      <c r="K1" t="s" s="10">
         <v>1423</v>
-      </c>
-      <c r="I1" t="s" s="10">
-        <v>1424</v>
-      </c>
-      <c r="J1" t="s" s="10">
-        <v>1425</v>
-      </c>
-      <c r="K1" t="s" s="10">
-        <v>1426</v>
       </c>
     </row>
     <row r="2">
       <c r="B2" t="s" s="9">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="C2" t="s" s="9">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="E2" t="n" s="9">
         <v>-1000.0</v>
